--- a/data dosen/Data dosen.xlsx
+++ b/data dosen/Data dosen.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\codingan\sem 7\magang\project\telkom-publication-dashboard\data dosen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6506C51-CC38-422A-B099-1D6BE4A0815C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AB98CA24-0FFB-433B-BEE7-E697C391E363}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4335"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$140</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="287">
   <si>
     <t>No</t>
   </si>
@@ -513,13 +512,403 @@
   </si>
   <si>
     <t>NIP</t>
+  </si>
+  <si>
+    <t>scholar_id</t>
+  </si>
+  <si>
+    <t>8kDg_v4AAAAJ</t>
+  </si>
+  <si>
+    <t>VdPx-dgAAAAJ</t>
+  </si>
+  <si>
+    <t>GHtaGbQAAAAJ</t>
+  </si>
+  <si>
+    <t>et_PgM0AAAAJ</t>
+  </si>
+  <si>
+    <t>IlzricYAAAAJ</t>
+  </si>
+  <si>
+    <t>fOTNsDEAAAAJ</t>
+  </si>
+  <si>
+    <t>5aJ1sg8AAAAJ</t>
+  </si>
+  <si>
+    <t>0RiyjfoAAAAJ</t>
+  </si>
+  <si>
+    <t>KJ41p44AAAAJ</t>
+  </si>
+  <si>
+    <t>DLHKVF4AAAAJ</t>
+  </si>
+  <si>
+    <t>A8RhhPsAAAAJ</t>
+  </si>
+  <si>
+    <t>KYooSqIAAAAJ</t>
+  </si>
+  <si>
+    <t>__yvF0YAAAAJ</t>
+  </si>
+  <si>
+    <t>WhgJqtMAAAAJ</t>
+  </si>
+  <si>
+    <t>DrKleQUAAAAJ</t>
+  </si>
+  <si>
+    <t>zGrZthcAAAAJ</t>
+  </si>
+  <si>
+    <t>zV5eEDEAAAAJ</t>
+  </si>
+  <si>
+    <t>HmvywroAAAAJ</t>
+  </si>
+  <si>
+    <t>7yhw4NkAAAAJ</t>
+  </si>
+  <si>
+    <t>NMxEzn0AAAAJ</t>
+  </si>
+  <si>
+    <t>Zfepb0sAAAAJ</t>
+  </si>
+  <si>
+    <t>JazHhjgAAAAJ</t>
+  </si>
+  <si>
+    <t>mDBDcbYAAAAJ</t>
+  </si>
+  <si>
+    <t>0kRNJKUAAAAJ</t>
+  </si>
+  <si>
+    <t>ieF2xcMAAAAJ</t>
+  </si>
+  <si>
+    <t>U_QPERsAAAAJ</t>
+  </si>
+  <si>
+    <t>9OYkLNUAAAAJ</t>
+  </si>
+  <si>
+    <t>ngd0MaEAAAAJ</t>
+  </si>
+  <si>
+    <t>YTJkW7IAAAAJ</t>
+  </si>
+  <si>
+    <t>Q5pO42EAAAAJ</t>
+  </si>
+  <si>
+    <t>4Nf9KBAAAAAJ</t>
+  </si>
+  <si>
+    <t>zx4OWkoAAAAJ</t>
+  </si>
+  <si>
+    <t>JLtfpacAAAAJ</t>
+  </si>
+  <si>
+    <t>nro_9rcAAAAJ</t>
+  </si>
+  <si>
+    <t>t37rnfsAAAAJ</t>
+  </si>
+  <si>
+    <t>zZ_Rgi4AAAAJ</t>
+  </si>
+  <si>
+    <t>nBBaQSsAAAAJ</t>
+  </si>
+  <si>
+    <t>fFD2dqsAAAAJ</t>
+  </si>
+  <si>
+    <t>dUiLgeoAAAAJ</t>
+  </si>
+  <si>
+    <t>ZqpaSjQAAAAJ</t>
+  </si>
+  <si>
+    <t>qLqQ3KgAAAAJ</t>
+  </si>
+  <si>
+    <t>eeGrqhMAAAAJ</t>
+  </si>
+  <si>
+    <t>dbXh_4MAAAAJ</t>
+  </si>
+  <si>
+    <t>UyQsg84AAAAJ</t>
+  </si>
+  <si>
+    <t>i3GFpqcAAAAJ</t>
+  </si>
+  <si>
+    <t>t460LKAAAAAJ</t>
+  </si>
+  <si>
+    <t>Sl6zKqYAAAAJ</t>
+  </si>
+  <si>
+    <t>EJxp5CwAAAAJ</t>
+  </si>
+  <si>
+    <t>orATboQAAAAJ</t>
+  </si>
+  <si>
+    <t>_dDsSrYAAAAJ</t>
+  </si>
+  <si>
+    <t>KRv_8nAAAAAJ</t>
+  </si>
+  <si>
+    <t>zobDzGMAAAAJ</t>
+  </si>
+  <si>
+    <t>HaelSx0AAAAJ</t>
+  </si>
+  <si>
+    <t>fHwnUQgAAAAJ</t>
+  </si>
+  <si>
+    <t>bDS0yjwAAAAJ</t>
+  </si>
+  <si>
+    <t>JxebffcAAAAJ</t>
+  </si>
+  <si>
+    <t>SnZZwd8AAAAJ</t>
+  </si>
+  <si>
+    <t>G0kxmiUAAAAJ</t>
+  </si>
+  <si>
+    <t>DY3h0kwAAAAJ</t>
+  </si>
+  <si>
+    <t>ekz8kCgAAAAJ</t>
+  </si>
+  <si>
+    <t>FeG9wHcAAAAJ</t>
+  </si>
+  <si>
+    <t>zwCyX-UAAAAJ</t>
+  </si>
+  <si>
+    <t>570oCT4AAAAJ</t>
+  </si>
+  <si>
+    <t>olCFmBAAAAAJ</t>
+  </si>
+  <si>
+    <t>8BQt9rIAAAAJ</t>
+  </si>
+  <si>
+    <t>oxsiEOMAAAAJ</t>
+  </si>
+  <si>
+    <t>boNkmYoAAAAJ</t>
+  </si>
+  <si>
+    <t>fWVfnhQAAAAJ</t>
+  </si>
+  <si>
+    <t>KHYfzqsAAAAJ</t>
+  </si>
+  <si>
+    <t>YxQhctcAAAAJ</t>
+  </si>
+  <si>
+    <t>NkJgzwkAAAAJ</t>
+  </si>
+  <si>
+    <t>-s8BtB0AAAAJ</t>
+  </si>
+  <si>
+    <t>8QtcDvUAAAAJ</t>
+  </si>
+  <si>
+    <t>IUbs8vAAAAAJ</t>
+  </si>
+  <si>
+    <t>JQHAA_wAAAAJ</t>
+  </si>
+  <si>
+    <t>bx43pp4AAAAJ</t>
+  </si>
+  <si>
+    <t>yHJo1fIAAAAJ</t>
+  </si>
+  <si>
+    <t>XzqWk8sAAAAJ</t>
+  </si>
+  <si>
+    <t>gRKMpbsAAAAJ</t>
+  </si>
+  <si>
+    <t>Wd9g3PIAAAAJ</t>
+  </si>
+  <si>
+    <t>e8O65_EAAAAJ</t>
+  </si>
+  <si>
+    <t>Ectwm8gAAAAJ</t>
+  </si>
+  <si>
+    <t>sjP7SiIAAAAJ</t>
+  </si>
+  <si>
+    <t>V34yb6gAAAAJ</t>
+  </si>
+  <si>
+    <t>C12lFx4AAAAJ</t>
+  </si>
+  <si>
+    <t>NUfgp0IAAAAJ</t>
+  </si>
+  <si>
+    <t>mMwVENwAAAAJ</t>
+  </si>
+  <si>
+    <t>7raoHVAAAAAJ</t>
+  </si>
+  <si>
+    <t>8IK9-44AAAAJ</t>
+  </si>
+  <si>
+    <t>b7mGuysAAAAJ</t>
+  </si>
+  <si>
+    <t>ltFcWtEAAAAJ</t>
+  </si>
+  <si>
+    <t>ild0R6EAAAAJ</t>
+  </si>
+  <si>
+    <t>mpmJE08AAAAJ</t>
+  </si>
+  <si>
+    <t>wtCLFy4AAAAJ</t>
+  </si>
+  <si>
+    <t>dPkEMOcAAAAJ</t>
+  </si>
+  <si>
+    <t>kRrlQmEAAAAJ</t>
+  </si>
+  <si>
+    <t>hqE5YwQAAAAJ</t>
+  </si>
+  <si>
+    <t>UUTgTtQAAAAJ</t>
+  </si>
+  <si>
+    <t>fdUSfVwAAAAJ</t>
+  </si>
+  <si>
+    <t>a2CrvckAAAAJ</t>
+  </si>
+  <si>
+    <t>7szZG-MAAAAJ</t>
+  </si>
+  <si>
+    <t>PiYosHQAAAAJ</t>
+  </si>
+  <si>
+    <t>Pm2sXBIAAAAJ</t>
+  </si>
+  <si>
+    <t>9Ons52gAAAAJ</t>
+  </si>
+  <si>
+    <t>yssM-SYAAAAJ</t>
+  </si>
+  <si>
+    <t>yjmpA7MAAAAJ</t>
+  </si>
+  <si>
+    <t>nxiZfxgAAAAJ</t>
+  </si>
+  <si>
+    <t>ogDb7tAAAAAJ</t>
+  </si>
+  <si>
+    <t>NyxtCnUAAAAJ</t>
+  </si>
+  <si>
+    <t>KQOhk3cAAAAJ</t>
+  </si>
+  <si>
+    <t>teos638AAAAJ</t>
+  </si>
+  <si>
+    <t>PTBxDlIAAAAJ</t>
+  </si>
+  <si>
+    <t>A0VuwJ8AAAAJ</t>
+  </si>
+  <si>
+    <t>vjhbCfQAAAAJ</t>
+  </si>
+  <si>
+    <t>SO77hlcAAAAJ</t>
+  </si>
+  <si>
+    <t>7MclnucAAAAJ</t>
+  </si>
+  <si>
+    <t>Fl4VBXUAAAAJ</t>
+  </si>
+  <si>
+    <t>ABRzvIsAAAAJ</t>
+  </si>
+  <si>
+    <t>GqSZi00AAAAJ</t>
+  </si>
+  <si>
+    <t>yVCOLCsAAAAJ</t>
+  </si>
+  <si>
+    <t>5-z7osEAAAAJ</t>
+  </si>
+  <si>
+    <t>9xOlvcwAAAAJ</t>
+  </si>
+  <si>
+    <t>CLh_rTAAAAAJ</t>
+  </si>
+  <si>
+    <t>NSxZt5sAAAAJ</t>
+  </si>
+  <si>
+    <t>5AAN8aIAAAAJ</t>
+  </si>
+  <si>
+    <t>-zWuOpYAAAAJ</t>
+  </si>
+  <si>
+    <t>M7FpO6QAAAAJ</t>
+  </si>
+  <si>
+    <t>-DQN8fcAAAAJ</t>
+  </si>
+  <si>
+    <t>a5SEJPkAAAAJ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,6 +920,19 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -556,7 +958,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -566,6 +968,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -900,19 +1317,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D223341-8E1C-4055-B39F-E5698F2A40DA}">
-  <dimension ref="A1:E140"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F140"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="3.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.7265625" style="2"/>
+    <col min="1" max="1" width="3.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="8.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -928,8 +1346,11 @@
       <c r="E1" s="3" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -945,8 +1366,11 @@
       <c r="E2" s="2">
         <v>25620001</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -962,8 +1386,11 @@
       <c r="E3" s="2">
         <v>19870005</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -979,8 +1406,11 @@
       <c r="E4" s="2">
         <v>19880005</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -996,8 +1426,11 @@
       <c r="E5" s="2">
         <v>19920005</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1013,8 +1446,11 @@
       <c r="E6" s="2">
         <v>19930001</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1030,8 +1466,11 @@
       <c r="E7" s="2">
         <v>19920002</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F7" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1047,8 +1486,11 @@
       <c r="E8" s="2">
         <v>19890002</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F8" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1064,8 +1506,11 @@
       <c r="E9" s="2">
         <v>20870006</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F9" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1081,8 +1526,11 @@
       <c r="E10" s="2">
         <v>19790001</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F10" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1098,8 +1546,11 @@
       <c r="E11" s="2">
         <v>19870002</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F11" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1115,8 +1566,11 @@
       <c r="E12" s="2">
         <v>19870004</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F12" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1132,8 +1586,11 @@
       <c r="E13" s="2">
         <v>19940002</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F13" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1149,8 +1606,11 @@
       <c r="E14" s="2">
         <v>19920003</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F14" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1166,25 +1626,28 @@
       <c r="E15" s="2">
         <v>19810001</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+      <c r="F15" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" s="5" customFormat="1">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="5">
         <v>19900002</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1200,8 +1663,11 @@
       <c r="E17" s="2">
         <v>19900004</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F17" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1217,25 +1683,31 @@
       <c r="E18" s="2">
         <v>17910092</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
+      <c r="F18" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="7" customFormat="1">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="C19" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="7">
         <v>19940001</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F19" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -1251,8 +1723,11 @@
       <c r="E20" s="2">
         <v>25780004</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -1268,8 +1743,11 @@
       <c r="E21" s="2">
         <v>19900003</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F21" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -1285,8 +1763,11 @@
       <c r="E22" s="2">
         <v>19920004</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F22" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -1302,8 +1783,11 @@
       <c r="E23" s="2">
         <v>19900008</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F23" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -1319,8 +1803,11 @@
       <c r="E24" s="2">
         <v>19880003</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F24" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -1336,8 +1823,11 @@
       <c r="E25" s="2">
         <v>19900006</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F25" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -1353,8 +1843,11 @@
       <c r="E26" s="2">
         <v>19900005</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F26" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -1370,8 +1863,11 @@
       <c r="E27" s="2">
         <v>20870004</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F27" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -1387,8 +1883,11 @@
       <c r="E28" s="2">
         <v>20860017</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F28" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -1404,25 +1903,28 @@
       <c r="E29" s="2">
         <v>20940001</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
+      <c r="F29" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" s="5" customFormat="1">
+      <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="C30" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="5">
         <v>20930033</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -1438,8 +1940,11 @@
       <c r="E31" s="2">
         <v>25920026</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F31" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -1455,8 +1960,11 @@
       <c r="E32" s="2">
         <v>20920036</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F32" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -1472,8 +1980,11 @@
       <c r="E33" s="2">
         <v>20930036</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F33" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -1489,8 +2000,11 @@
       <c r="E34" s="2">
         <v>20860014</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F34" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -1506,8 +2020,11 @@
       <c r="E35" s="2">
         <v>20830012</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F35" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -1523,8 +2040,11 @@
       <c r="E36" s="2">
         <v>19900001</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F36" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -1540,8 +2060,11 @@
       <c r="E37" s="2">
         <v>20920039</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F37" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -1557,8 +2080,11 @@
       <c r="E38" s="2">
         <v>20930043</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F38" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -1574,8 +2100,11 @@
       <c r="E39" s="2">
         <v>23929009</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F39" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -1591,8 +2120,11 @@
       <c r="E40" s="2">
         <v>23890011</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F40" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -1608,8 +2140,11 @@
       <c r="E41" s="2">
         <v>19750005</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F41" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -1625,8 +2160,11 @@
       <c r="E42" s="2">
         <v>20910025</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F42" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -1642,8 +2180,11 @@
       <c r="E43" s="2">
         <v>22730002</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F43" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -1659,8 +2200,11 @@
       <c r="E44" s="2">
         <v>23880010</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F44" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -1676,8 +2220,11 @@
       <c r="E45" s="2">
         <v>23900009</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F45" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -1693,8 +2240,11 @@
       <c r="E46" s="2">
         <v>24930005</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F46" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -1705,13 +2255,16 @@
         <v>5</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="E47" s="2">
         <v>25950031</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F47" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -1727,8 +2280,11 @@
       <c r="E48" s="2">
         <v>25940031</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F48" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -1744,8 +2300,11 @@
       <c r="E49" s="2">
         <v>23950024</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F49" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -1761,8 +2320,11 @@
       <c r="E50" s="2">
         <v>25970012</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F50" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -1778,8 +2340,11 @@
       <c r="E51" s="2">
         <v>25940030</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F51" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -1795,8 +2360,11 @@
       <c r="E52" s="2">
         <v>23950023</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F52" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -1812,8 +2380,11 @@
       <c r="E53" s="2">
         <v>25930030</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F53" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -1829,8 +2400,11 @@
       <c r="E54" s="2">
         <v>24950003</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F54" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -1846,8 +2420,11 @@
       <c r="E55" s="2">
         <v>25930031</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F55" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -1863,8 +2440,11 @@
       <c r="E56" s="2">
         <v>25910023</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F56" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -1880,8 +2460,11 @@
       <c r="E57" s="2">
         <v>21890010</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F57" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -1897,8 +2480,11 @@
       <c r="E58" s="2">
         <v>21910012</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F58" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -1914,8 +2500,11 @@
       <c r="E59" s="2">
         <v>21870007</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F59" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -1931,8 +2520,11 @@
       <c r="E60" s="2">
         <v>22960009</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F60" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -1948,8 +2540,11 @@
       <c r="E61" s="2">
         <v>22960008</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F61" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -1965,8 +2560,11 @@
       <c r="E62" s="2">
         <v>22900008</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F62" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -1982,8 +2580,11 @@
       <c r="E63" s="2">
         <v>22970007</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F63" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -1999,8 +2600,11 @@
       <c r="E64" s="2">
         <v>22940003</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F64" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -2016,8 +2620,11 @@
       <c r="E65" s="2">
         <v>22930003</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F65" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -2033,8 +2640,11 @@
       <c r="E66" s="2">
         <v>15890076</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F66" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -2050,8 +2660,11 @@
       <c r="E67" s="2">
         <v>23850011</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F67" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -2067,8 +2680,11 @@
       <c r="E68" s="2">
         <v>22960010</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F68" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -2084,8 +2700,11 @@
       <c r="E69" s="2">
         <v>22920004</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F69" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -2101,8 +2720,11 @@
       <c r="E70" s="2">
         <v>15720039</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F70" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -2118,8 +2740,11 @@
       <c r="E71" s="2">
         <v>22940040</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F71" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -2135,8 +2760,11 @@
       <c r="E72" s="2">
         <v>22960061</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F72" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -2152,8 +2780,11 @@
       <c r="E73" s="2">
         <v>22950050</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F73" s="8" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -2169,8 +2800,11 @@
       <c r="E74" s="2">
         <v>22900033</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F74" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -2186,8 +2820,11 @@
       <c r="E75" s="2">
         <v>22930045</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F75" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -2203,8 +2840,11 @@
       <c r="E76" s="2">
         <v>22970043</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F76" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -2220,8 +2860,11 @@
       <c r="E77" s="2">
         <v>22820015</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F77" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -2237,8 +2880,11 @@
       <c r="E78" s="2">
         <v>22950049</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F78" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -2254,8 +2900,11 @@
       <c r="E79" s="2">
         <v>22920034</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F79" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -2271,8 +2920,11 @@
       <c r="E80" s="2">
         <v>22950051</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F80" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -2288,8 +2940,11 @@
       <c r="E81" s="2">
         <v>22960060</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F81" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -2305,8 +2960,11 @@
       <c r="E82" s="2">
         <v>21950014</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F82" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -2322,8 +2980,11 @@
       <c r="E83" s="2">
         <v>22970044</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F83" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -2339,8 +3000,11 @@
       <c r="E84" s="2">
         <v>22980046</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F84" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -2356,8 +3020,11 @@
       <c r="E85" s="2">
         <v>9820030</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F85" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -2373,8 +3040,11 @@
       <c r="E86" s="2">
         <v>26900002</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F86" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -2390,8 +3060,11 @@
       <c r="E87" s="2">
         <v>22940041</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F87" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -2407,8 +3080,11 @@
       <c r="E88" s="2">
         <v>25760006</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F88" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -2424,8 +3100,11 @@
       <c r="E89" s="2">
         <v>20900019</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F89" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -2441,8 +3120,11 @@
       <c r="E90" s="2">
         <v>23970026</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F90" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -2458,8 +3140,11 @@
       <c r="E91" s="2">
         <v>23990020</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F91" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -2475,8 +3160,11 @@
       <c r="E92" s="2">
         <v>23900007</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F92" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -2492,8 +3180,11 @@
       <c r="E93" s="2">
         <v>23970024</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F93" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -2509,8 +3200,11 @@
       <c r="E94" s="2">
         <v>23960023</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F94" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -2526,8 +3220,11 @@
       <c r="E95" s="2">
         <v>23910008</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F95" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -2543,8 +3240,11 @@
       <c r="E96" s="2">
         <v>23990019</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F96" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -2560,8 +3260,11 @@
       <c r="E97" s="2">
         <v>23950016</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F97" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -2577,8 +3280,11 @@
       <c r="E98" s="2">
         <v>23980024</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F98" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -2594,8 +3300,11 @@
       <c r="E99" s="2">
         <v>22970009</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F99" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -2611,8 +3320,11 @@
       <c r="E100" s="2">
         <v>22950019</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F100" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -2628,8 +3340,11 @@
       <c r="E101" s="2">
         <v>23900006</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F101" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -2645,8 +3360,11 @@
       <c r="E102" s="2">
         <v>24970010</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F102" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -2662,8 +3380,11 @@
       <c r="E103" s="2">
         <v>24980018</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F103" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -2679,8 +3400,11 @@
       <c r="E104" s="2">
         <v>24800005</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F104" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -2696,25 +3420,28 @@
       <c r="E105" s="2">
         <v>25820001</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A106" s="1">
+      <c r="F105" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" s="5" customFormat="1">
+      <c r="A106" s="4">
         <v>105</v>
       </c>
-      <c r="B106" s="2" t="s">
+      <c r="B106" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C106" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D106" s="2" t="s">
+      <c r="C106" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D106" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E106" s="2">
+      <c r="E106" s="5">
         <v>25950003</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -2730,8 +3457,11 @@
       <c r="E107" s="2">
         <v>25990003</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F107" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -2747,8 +3477,11 @@
       <c r="E108" s="2">
         <v>25010008</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F108" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -2764,8 +3497,11 @@
       <c r="E109" s="2">
         <v>25900003</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F109" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -2781,8 +3517,11 @@
       <c r="E110" s="2">
         <v>25989002</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F110" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -2798,25 +3537,28 @@
       <c r="E111" s="2">
         <v>23920006</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A112" s="1">
+      <c r="F111" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" s="5" customFormat="1">
+      <c r="A112" s="4">
         <v>111</v>
       </c>
-      <c r="B112" s="2" t="s">
+      <c r="B112" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D112" s="2" t="s">
+      <c r="C112" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E112" s="2">
+      <c r="E112" s="5">
         <v>25010028</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -2832,8 +3574,11 @@
       <c r="E113" s="2">
         <v>25990026</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F113" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -2849,8 +3594,11 @@
       <c r="E114" s="2">
         <v>25000022</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F114" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -2866,8 +3614,11 @@
       <c r="E115" s="2">
         <v>25010029</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F115" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -2883,8 +3634,11 @@
       <c r="E116" s="2">
         <v>25970019</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F116" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -2900,8 +3654,11 @@
       <c r="E117" s="2">
         <v>25980022</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F117" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -2917,8 +3674,11 @@
       <c r="E118" s="2">
         <v>25010040</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F118" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -2934,8 +3694,11 @@
       <c r="E119" s="2">
         <v>25980028</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F119" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -2951,8 +3714,11 @@
       <c r="E120" s="2">
         <v>25950039</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F120" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -2968,8 +3734,11 @@
       <c r="E121" s="2">
         <v>25000029</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F121" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -2985,8 +3754,11 @@
       <c r="E122" s="2">
         <v>1760006</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F122" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -3002,8 +3774,11 @@
       <c r="E123" s="2">
         <v>26020011</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F123" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -3019,8 +3794,11 @@
       <c r="E124" s="2">
         <v>26800006</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F124" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -3036,8 +3814,11 @@
       <c r="E125" s="2">
         <v>26980037</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F125" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -3053,8 +3834,11 @@
       <c r="E126" s="2">
         <v>26010022</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F126" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -3070,8 +3854,11 @@
       <c r="E127" s="2">
         <v>26990042</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F127" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -3087,42 +3874,45 @@
       <c r="E128" s="2">
         <v>20950002</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A129" s="1">
+      <c r="F128" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" s="5" customFormat="1">
+      <c r="A129" s="4">
         <v>128</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C129" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D129" s="2" t="s">
+      <c r="C129" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E129" s="2">
+      <c r="E129" s="5">
         <v>26990054</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A130" s="1">
+    <row r="130" spans="1:6" s="5" customFormat="1">
+      <c r="A130" s="4">
         <v>129</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="C130" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D130" s="2" t="s">
+      <c r="C130" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E130" s="2">
+      <c r="E130" s="5">
         <v>26020022</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -3138,42 +3928,45 @@
       <c r="E131" s="2">
         <v>26960026</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A132" s="1">
+      <c r="F131" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" s="5" customFormat="1">
+      <c r="A132" s="4">
         <v>131</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D132" s="2" t="s">
+      <c r="C132" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D132" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E132" s="2">
+      <c r="E132" s="5">
         <v>26020021</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A133" s="1">
+    <row r="133" spans="1:6" s="5" customFormat="1">
+      <c r="A133" s="4">
         <v>132</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D133" s="2" t="s">
+      <c r="C133" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E133" s="2">
+      <c r="E133" s="5">
         <v>26980042</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -3189,8 +3982,11 @@
       <c r="E134" s="2">
         <v>24960014</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F134" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -3206,8 +4002,11 @@
       <c r="E135" s="2">
         <v>26990061</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F135" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -3223,25 +4022,28 @@
       <c r="E136" s="2">
         <v>26000068</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A137" s="1">
+      <c r="F136" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" s="5" customFormat="1">
+      <c r="A137" s="4">
         <v>136</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="C137" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D137" s="2" t="s">
+      <c r="C137" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D137" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E137" s="2">
+      <c r="E137" s="5">
         <v>26020038</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -3257,8 +4059,11 @@
       <c r="E138" s="2">
         <v>26000067</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F138" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -3274,8 +4079,11 @@
       <c r="E139" s="2">
         <v>26900011</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F139" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -3291,9 +4099,11 @@
       <c r="E140" s="2">
         <v>26830001</v>
       </c>
+      <c r="F140" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E140" xr:uid="{9D223341-8E1C-4055-B39F-E5698F2A40DA}"/>
+  <autoFilter ref="A1:E140"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>